--- a/Copper/4. Exploratory data analysis/Normality_checks.xlsx
+++ b/Copper/4. Exploratory data analysis/Normality_checks.xlsx
@@ -1,465 +1,472 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Copper/4. Exploratory data analysis/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_DA2568B94F70E0618C506E6D10B6BB7C338ED19D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E396FE0E-9D81-418A-82B7-0FD01BD12580}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HA10_CS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HA10_OS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="HA80_CS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="HA10_CS" sheetId="1" r:id="rId1"/>
+    <sheet name="HA10_OS" sheetId="2" r:id="rId2"/>
+    <sheet name="HA80_CS" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
-  <si>
-    <t xml:space="preserve">Variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skewness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relative_elevation_m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dist_from_EFPC_km</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drainage_area_km2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed_lulc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temp_C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOC_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mg_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIC_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free_Cu_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuOH_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_OH_2_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuSO4_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_CO3_2_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuCl_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuHCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Cu_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Cu_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_CuOH_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Ca_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_H_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Mg_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Na_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2_CO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HS_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2S_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgHCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgSO4_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaHCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaCO3_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaSO4_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_H_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Ca_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Mg_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Na_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_K_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Acute_Tox_Daphnia_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Acute_Tox_Minnow_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Chronic_Tox_Daphnia_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Chronic_Tox_Minnow_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOC_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOC_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ca_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mg_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mg_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO4_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cl_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIC_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIC_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free_Cu_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free_Cu_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuOH_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuOH_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_OH_2_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_OH_2_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuSO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuSO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_CO3_2_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_CO3_2_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuCl_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuCl_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuHCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CuHCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Cu_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Cu_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2_CO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2_CO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HS_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HS_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2S_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2S_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgHCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgHCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgSO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MgSO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaHCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaHCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaCO3_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaCO3_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaSO4_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CaSO4_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_H_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_H_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Ca_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Ca_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Mg_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Mg_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Na_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_Na_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_K_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOrg_K_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Acute_Tox_Daphnia_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Acute_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Acute_Tox_Minnow_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Acute_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Chronic_Tox_Daphnia_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Chronic_Tox_Daphnia_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Chronic_Tox_Minnow_uM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu_Chronic_Tox_Minnow_nM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Cu_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Cu_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_CuOH_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_CuOH_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Ca_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Ca_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_H_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_H_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Mg_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Mg_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Na_nmol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BL_Na_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBL_Cu_nmol_g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBL_Cu_mol_kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rel_prop_Cu</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="146">
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Normality</t>
+  </si>
+  <si>
+    <t>Skewness</t>
+  </si>
+  <si>
+    <t>Relative_elevation_m</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Dist_from_EFPC_km</t>
+  </si>
+  <si>
+    <t>Drainage_area_km2</t>
+  </si>
+  <si>
+    <t>Developed_lulc</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>Temp_C</t>
+  </si>
+  <si>
+    <t>DOC_uM</t>
+  </si>
+  <si>
+    <t>Ca_uM</t>
+  </si>
+  <si>
+    <t>Mg_uM</t>
+  </si>
+  <si>
+    <t>Na_uM</t>
+  </si>
+  <si>
+    <t>K_uM</t>
+  </si>
+  <si>
+    <t>SO4_uM</t>
+  </si>
+  <si>
+    <t>Cl_uM</t>
+  </si>
+  <si>
+    <t>DIC_uM</t>
+  </si>
+  <si>
+    <t>Zn_uM</t>
+  </si>
+  <si>
+    <t>Cu_uM</t>
+  </si>
+  <si>
+    <t>Free_Cu_M</t>
+  </si>
+  <si>
+    <t>CuOH_M</t>
+  </si>
+  <si>
+    <t>Cu_OH_2_M</t>
+  </si>
+  <si>
+    <t>CuSO4_M</t>
+  </si>
+  <si>
+    <t>CuCO3_M</t>
+  </si>
+  <si>
+    <t>Cu_CO3_2_M</t>
+  </si>
+  <si>
+    <t>CuCl_M</t>
+  </si>
+  <si>
+    <t>CuHCO3_M</t>
+  </si>
+  <si>
+    <t>TOrg_Cu_M</t>
+  </si>
+  <si>
+    <t>BL_Cu_mol_kg</t>
+  </si>
+  <si>
+    <t>BL_CuOH_mol_kg</t>
+  </si>
+  <si>
+    <t>BL_Ca_mol_kg</t>
+  </si>
+  <si>
+    <t>BL_H_mol_kg</t>
+  </si>
+  <si>
+    <t>BL_Mg_mol_kg</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>BL_Na_mol_kg</t>
+  </si>
+  <si>
+    <t>HCO3_M</t>
+  </si>
+  <si>
+    <t>H2_CO3_M</t>
+  </si>
+  <si>
+    <t>HS_M</t>
+  </si>
+  <si>
+    <t>H2S_M</t>
+  </si>
+  <si>
+    <t>MgHCO3_M</t>
+  </si>
+  <si>
+    <t>MgCO3_M</t>
+  </si>
+  <si>
+    <t>MgSO4_M</t>
+  </si>
+  <si>
+    <t>CaHCO3_M</t>
+  </si>
+  <si>
+    <t>CaCO3_M</t>
+  </si>
+  <si>
+    <t>CaSO4_M</t>
+  </si>
+  <si>
+    <t>TOrg_H_M</t>
+  </si>
+  <si>
+    <t>TOrg_Ca_M</t>
+  </si>
+  <si>
+    <t>TOrg_Mg_M</t>
+  </si>
+  <si>
+    <t>TOrg_Na_M</t>
+  </si>
+  <si>
+    <t>TOrg_K_M</t>
+  </si>
+  <si>
+    <t>Cu_Acute_Tox_Daphnia_M</t>
+  </si>
+  <si>
+    <t>Cu_Acute_Tox_Minnow_M</t>
+  </si>
+  <si>
+    <t>Cu_Chronic_Tox_Daphnia_M</t>
+  </si>
+  <si>
+    <t>Cu_Chronic_Tox_Minnow_M</t>
+  </si>
+  <si>
+    <t>DOC_M</t>
+  </si>
+  <si>
+    <t>DOC_nM</t>
+  </si>
+  <si>
+    <t>Ca_M</t>
+  </si>
+  <si>
+    <t>Ca_nM</t>
+  </si>
+  <si>
+    <t>Mg_M</t>
+  </si>
+  <si>
+    <t>Mg_nM</t>
+  </si>
+  <si>
+    <t>Na_M</t>
+  </si>
+  <si>
+    <t>Na_nM</t>
+  </si>
+  <si>
+    <t>K_M</t>
+  </si>
+  <si>
+    <t>K_nM</t>
+  </si>
+  <si>
+    <t>SO4_M</t>
+  </si>
+  <si>
+    <t>SO4_nM</t>
+  </si>
+  <si>
+    <t>Cl_M</t>
+  </si>
+  <si>
+    <t>Cl_nM</t>
+  </si>
+  <si>
+    <t>DIC_M</t>
+  </si>
+  <si>
+    <t>DIC_nM</t>
+  </si>
+  <si>
+    <t>Zn_M</t>
+  </si>
+  <si>
+    <t>Zn_nM</t>
+  </si>
+  <si>
+    <t>Cu_M</t>
+  </si>
+  <si>
+    <t>Cu_nM</t>
+  </si>
+  <si>
+    <t>Free_Cu_uM</t>
+  </si>
+  <si>
+    <t>Free_Cu_nM</t>
+  </si>
+  <si>
+    <t>CuOH_uM</t>
+  </si>
+  <si>
+    <t>CuOH_nM</t>
+  </si>
+  <si>
+    <t>Cu_OH_2_uM</t>
+  </si>
+  <si>
+    <t>Cu_OH_2_nM</t>
+  </si>
+  <si>
+    <t>CuSO4_uM</t>
+  </si>
+  <si>
+    <t>CuSO4_nM</t>
+  </si>
+  <si>
+    <t>CuCO3_uM</t>
+  </si>
+  <si>
+    <t>CuCO3_nM</t>
+  </si>
+  <si>
+    <t>Cu_CO3_2_uM</t>
+  </si>
+  <si>
+    <t>Cu_CO3_2_nM</t>
+  </si>
+  <si>
+    <t>CuCl_uM</t>
+  </si>
+  <si>
+    <t>CuCl_nM</t>
+  </si>
+  <si>
+    <t>CuHCO3_uM</t>
+  </si>
+  <si>
+    <t>CuHCO3_nM</t>
+  </si>
+  <si>
+    <t>TOrg_Cu_uM</t>
+  </si>
+  <si>
+    <t>TOrg_Cu_nM</t>
+  </si>
+  <si>
+    <t>HCO3_uM</t>
+  </si>
+  <si>
+    <t>HCO3_nM</t>
+  </si>
+  <si>
+    <t>H2_CO3_uM</t>
+  </si>
+  <si>
+    <t>H2_CO3_nM</t>
+  </si>
+  <si>
+    <t>HS_uM</t>
+  </si>
+  <si>
+    <t>HS_nM</t>
+  </si>
+  <si>
+    <t>H2S_uM</t>
+  </si>
+  <si>
+    <t>H2S_nM</t>
+  </si>
+  <si>
+    <t>MgHCO3_uM</t>
+  </si>
+  <si>
+    <t>MgHCO3_nM</t>
+  </si>
+  <si>
+    <t>MgCO3_uM</t>
+  </si>
+  <si>
+    <t>MgCO3_nM</t>
+  </si>
+  <si>
+    <t>MgSO4_uM</t>
+  </si>
+  <si>
+    <t>MgSO4_nM</t>
+  </si>
+  <si>
+    <t>CaHCO3_uM</t>
+  </si>
+  <si>
+    <t>CaHCO3_nM</t>
+  </si>
+  <si>
+    <t>CaCO3_uM</t>
+  </si>
+  <si>
+    <t>CaCO3_nM</t>
+  </si>
+  <si>
+    <t>CaSO4_uM</t>
+  </si>
+  <si>
+    <t>CaSO4_nM</t>
+  </si>
+  <si>
+    <t>TOrg_H_uM</t>
+  </si>
+  <si>
+    <t>TOrg_H_nM</t>
+  </si>
+  <si>
+    <t>TOrg_Ca_uM</t>
+  </si>
+  <si>
+    <t>TOrg_Ca_nM</t>
+  </si>
+  <si>
+    <t>TOrg_Mg_uM</t>
+  </si>
+  <si>
+    <t>TOrg_Mg_nM</t>
+  </si>
+  <si>
+    <t>TOrg_Na_uM</t>
+  </si>
+  <si>
+    <t>TOrg_Na_nM</t>
+  </si>
+  <si>
+    <t>TOrg_K_uM</t>
+  </si>
+  <si>
+    <t>TOrg_K_nM</t>
+  </si>
+  <si>
+    <t>Cu_Acute_Tox_Daphnia_uM</t>
+  </si>
+  <si>
+    <t>Cu_Acute_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t>Cu_Acute_Tox_Minnow_uM</t>
+  </si>
+  <si>
+    <t>Cu_Acute_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t>Cu_Chronic_Tox_Daphnia_uM</t>
+  </si>
+  <si>
+    <t>Cu_Chronic_Tox_Daphnia_nM</t>
+  </si>
+  <si>
+    <t>Cu_Chronic_Tox_Minnow_uM</t>
+  </si>
+  <si>
+    <t>Cu_Chronic_Tox_Minnow_nM</t>
+  </si>
+  <si>
+    <t>BL_Cu_nmol_kg</t>
+  </si>
+  <si>
+    <t>BL_Cu_nmol_g</t>
+  </si>
+  <si>
+    <t>BL_CuOH_nmol_kg</t>
+  </si>
+  <si>
+    <t>BL_CuOH_nmol_g</t>
+  </si>
+  <si>
+    <t>BL_Ca_nmol_kg</t>
+  </si>
+  <si>
+    <t>BL_Ca_nmol_g</t>
+  </si>
+  <si>
+    <t>BL_H_nmol_kg</t>
+  </si>
+  <si>
+    <t>BL_H_nmol_g</t>
+  </si>
+  <si>
+    <t>BL_Mg_nmol_kg</t>
+  </si>
+  <si>
+    <t>BL_Mg_nmol_g</t>
+  </si>
+  <si>
+    <t>BL_Na_nmol_kg</t>
+  </si>
+  <si>
+    <t>BL_Na_nmol_g</t>
+  </si>
+  <si>
+    <t>TBL_Cu_nmol_g</t>
+  </si>
+  <si>
+    <t>TBL_Cu_mol_kg</t>
+  </si>
+  <si>
+    <t>rel_prop_Cu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -495,6 +502,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -776,11 +792,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C142"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -791,1569 +810,1569 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
-        <v>2.17301857884221</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2">
+        <v>2.1730185788422101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.781738678603504</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3">
+        <v>0.78173867860350399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="n">
-        <v>2.00686335405664</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4">
+        <v>2.0068633540566401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.866162986482195</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="C5">
+        <v>-0.86616298648219503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.262112805386116</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6">
+        <v>0.26211280538611598</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.189389410759909</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
-        <v>-0.534352395703904</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="C9">
+        <v>-0.53435239570390403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
-        <v>-0.296160296305932</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10">
+        <v>-0.29616029630593199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="C12">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>-0.614198152259788</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C15">
+        <v>-0.61419815225978802</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
-      <c r="C16" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="C16">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
-      <c r="C17" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="C17">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
-      <c r="C18" t="n">
-        <v>6.02214938482324</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="C18">
+        <v>6.0221493848232397</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" t="n">
-        <v>5.53806727723032</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="C19">
+        <v>5.5380672772303203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>10.9584883273681</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>6.75239888957468</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
-      <c r="C22" t="n">
-        <v>4.80955164594881</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22">
+        <v>4.8095516459488099</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
-        <v>9.54566911081435</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="C23">
+        <v>9.5456691108143499</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>5.96366330447536</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
-      <c r="C25" t="n">
-        <v>6.11510140815208</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="C25">
+        <v>6.1151014081520803</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
-      <c r="C26" t="n">
-        <v>4.25676852290332</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="C26">
+        <v>4.2567685229033199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
       </c>
-      <c r="C27" t="n">
-        <v>6.4059423578104</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="C27">
+        <v>6.4059423578103996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
-        <v>5.20539976059761</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="C28">
+        <v>5.2053997605976097</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>-1.49287600656777</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>15.6290628006312</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
-      <c r="C31" t="n">
-        <v>0.0211080552499912</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="C31">
+        <v>2.1108055249991198E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
-      <c r="C32" t="n">
-        <v>1.62190869151043</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="C32">
+        <v>1.6219086915104299</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
-      <c r="C33" t="n">
-        <v>-0.66455010684609</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="C33">
+        <v>-0.66455010684608995</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
-      <c r="C34" t="n">
-        <v>2.47410444509397</v>
-      </c>
-    </row>
-    <row r="35">
+      <c r="C34">
+        <v>2.4741044450939702</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
-      <c r="C35" t="n">
-        <v>-1.37896671332892</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="C35">
+        <v>-1.3789667133289201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>1.37299944593962</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
-      <c r="C37" t="n">
-        <v>0.252845558896645</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="C37">
+        <v>0.25284555889664501</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
       </c>
-      <c r="C38" t="n">
-        <v>7.37484442241642</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="C38">
+        <v>7.3748444224164196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
       </c>
-      <c r="C39" t="n">
-        <v>1.77299290182452</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="C39">
+        <v>1.7729929018245201</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>0.174553524203547</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
         <v>4</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>7.20714254936318</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>1.00468046453229</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
-      <c r="C43" t="n">
-        <v>4.28973622978728</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="C43">
+        <v>4.2897362297872803</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>3.25676851872266</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
       </c>
-      <c r="C45" t="n">
-        <v>3.46023014590009</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="C45">
+        <v>3.4602301459000899</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
       </c>
-      <c r="C46" t="n">
-        <v>13.6460054841937</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="C46">
+        <v>13.646005484193701</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
       </c>
-      <c r="C47" t="n">
-        <v>16.4225834144549</v>
-      </c>
-    </row>
-    <row r="48">
+      <c r="C47">
+        <v>16.422583414454898</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
         <v>4</v>
       </c>
-      <c r="C48" t="n">
-        <v>1.94733976280201</v>
-      </c>
-    </row>
-    <row r="49">
+      <c r="C48">
+        <v>1.9473397628020099</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
       </c>
-      <c r="C49" t="n">
-        <v>2.02758913840313</v>
-      </c>
-    </row>
-    <row r="50">
+      <c r="C49">
+        <v>2.0275891384031302</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
         <v>4</v>
       </c>
-      <c r="C50" t="n">
-        <v>2.49107590122785</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="C50">
+        <v>2.4910759012278501</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
         <v>4</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>1.92674379251941</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
       </c>
-      <c r="C52" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="C52">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="C53">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
         <v>4</v>
       </c>
-      <c r="C54" t="n">
-        <v>-0.534352395703903</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="C54">
+        <v>-0.53435239570390303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
         <v>4</v>
       </c>
-      <c r="C55" t="n">
-        <v>-0.534352395703905</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="C55">
+        <v>-0.53435239570390503</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
-      <c r="C56" t="n">
-        <v>-0.296160296305932</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="C56">
+        <v>-0.29616029630593199</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
         <v>4</v>
       </c>
-      <c r="C57" t="n">
-        <v>-0.296160296305931</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="C57">
+        <v>-0.29616029630593099</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
         <v>4</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
         <v>4</v>
       </c>
-      <c r="C60" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="C60">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
       </c>
-      <c r="C61" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="62">
+      <c r="C61">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
         <v>4</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
         <v>4</v>
       </c>
-      <c r="C66" t="n">
-        <v>-0.614198152259787</v>
-      </c>
-    </row>
-    <row r="67">
+      <c r="C66">
+        <v>-0.61419815225978702</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
         <v>4</v>
       </c>
-      <c r="C67" t="n">
-        <v>-0.614198152259787</v>
-      </c>
-    </row>
-    <row r="68">
+      <c r="C67">
+        <v>-0.61419815225978702</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
       </c>
-      <c r="C68" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="69">
+      <c r="C68">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
       </c>
-      <c r="C69" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="70">
+      <c r="C69">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
-      <c r="C70" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="C70">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
       </c>
-      <c r="C71" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="72">
+      <c r="C71">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
         <v>4</v>
       </c>
-      <c r="C72" t="n">
-        <v>6.02214938482324</v>
-      </c>
-    </row>
-    <row r="73">
+      <c r="C72">
+        <v>6.0221493848232397</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
-      <c r="C73" t="n">
-        <v>6.02214938482324</v>
-      </c>
-    </row>
-    <row r="74">
+      <c r="C73">
+        <v>6.0221493848232397</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
       </c>
-      <c r="C74" t="n">
-        <v>5.53806727723032</v>
-      </c>
-    </row>
-    <row r="75">
+      <c r="C74">
+        <v>5.5380672772303203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
       </c>
-      <c r="C75" t="n">
-        <v>5.53806727723032</v>
-      </c>
-    </row>
-    <row r="76">
+      <c r="C75">
+        <v>5.5380672772303203</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>10.9584883273681</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>10.9584883273681</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>6.75239888957468</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>6.75239888957468</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
-      <c r="C80" t="n">
-        <v>4.80955164594881</v>
-      </c>
-    </row>
-    <row r="81">
+      <c r="C80">
+        <v>4.8095516459488099</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
-      <c r="C81" t="n">
-        <v>4.80955164594881</v>
-      </c>
-    </row>
-    <row r="82">
+      <c r="C81">
+        <v>4.8095516459488099</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
-      <c r="C82" t="n">
-        <v>9.54566911081435</v>
-      </c>
-    </row>
-    <row r="83">
+      <c r="C82">
+        <v>9.5456691108143499</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
-      <c r="C83" t="n">
-        <v>9.54566911081435</v>
-      </c>
-    </row>
-    <row r="84">
+      <c r="C83">
+        <v>9.5456691108143499</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>5.96366330447536</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>5.96366330447536</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
-      <c r="C86" t="n">
-        <v>6.11510140815208</v>
-      </c>
-    </row>
-    <row r="87">
+      <c r="C86">
+        <v>6.1151014081520803</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
-      <c r="C87" t="n">
-        <v>6.11510140815208</v>
-      </c>
-    </row>
-    <row r="88">
+      <c r="C87">
+        <v>6.1151014081520803</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
-      <c r="C88" t="n">
-        <v>4.25676852290331</v>
-      </c>
-    </row>
-    <row r="89">
+      <c r="C88">
+        <v>4.2567685229033101</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
-      <c r="C89" t="n">
-        <v>4.25676852290331</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="C89">
+        <v>4.2567685229033101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
       </c>
-      <c r="C90" t="n">
-        <v>-0.66455010684609</v>
-      </c>
-    </row>
-    <row r="91">
+      <c r="C90">
+        <v>-0.66455010684608995</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
       </c>
-      <c r="C91" t="n">
-        <v>-0.66455010684609</v>
-      </c>
-    </row>
-    <row r="92">
+      <c r="C91">
+        <v>-0.66455010684608995</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
       </c>
-      <c r="C92" t="n">
-        <v>2.47410444509397</v>
-      </c>
-    </row>
-    <row r="93">
+      <c r="C92">
+        <v>2.4741044450939702</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
       </c>
-      <c r="C93" t="n">
-        <v>2.47410444509397</v>
-      </c>
-    </row>
-    <row r="94">
+      <c r="C93">
+        <v>2.4741044450939702</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
-      <c r="C94" t="n">
-        <v>-1.37896671332892</v>
-      </c>
-    </row>
-    <row r="95">
+      <c r="C94">
+        <v>-1.3789667133289201</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
-      <c r="C95" t="n">
-        <v>-1.37896671332892</v>
-      </c>
-    </row>
-    <row r="96">
+      <c r="C95">
+        <v>-1.3789667133289201</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>1.37299944593962</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>1.37299944593962</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
       </c>
-      <c r="C98" t="n">
-        <v>0.252845558896646</v>
-      </c>
-    </row>
-    <row r="99">
+      <c r="C98">
+        <v>0.25284555889664601</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
       </c>
-      <c r="C99" t="n">
-        <v>0.252845558896646</v>
-      </c>
-    </row>
-    <row r="100">
+      <c r="C99">
+        <v>0.25284555889664601</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100" t="s">
         <v>4</v>
       </c>
-      <c r="C100" t="n">
-        <v>7.37484442241641</v>
-      </c>
-    </row>
-    <row r="101">
+      <c r="C100">
+        <v>7.3748444224164098</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>104</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
       </c>
-      <c r="C101" t="n">
-        <v>7.37484442241642</v>
-      </c>
-    </row>
-    <row r="102">
+      <c r="C101">
+        <v>7.3748444224164196</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>105</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
       </c>
-      <c r="C102" t="n">
-        <v>1.77299290182452</v>
-      </c>
-    </row>
-    <row r="103">
+      <c r="C102">
+        <v>1.7729929018245201</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>106</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
       </c>
-      <c r="C103" t="n">
-        <v>1.77299290182452</v>
-      </c>
-    </row>
-    <row r="104">
+      <c r="C103">
+        <v>1.7729929018245201</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>107</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104">
         <v>0.174553524203547</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>108</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105">
         <v>0.174553524203547</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>109</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106">
         <v>7.20714254936318</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>110</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107">
         <v>7.20714254936318</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>111</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>1.00468046453229</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>112</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109">
         <v>1.00468046453229</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>113</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
-      <c r="C110" t="n">
-        <v>4.28973622978728</v>
-      </c>
-    </row>
-    <row r="111">
+      <c r="C110">
+        <v>4.2897362297872803</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>114</v>
       </c>
       <c r="B111" t="s">
         <v>4</v>
       </c>
-      <c r="C111" t="n">
-        <v>4.28973622978728</v>
-      </c>
-    </row>
-    <row r="112">
+      <c r="C111">
+        <v>4.2897362297872803</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>115</v>
       </c>
       <c r="B112" t="s">
         <v>4</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112">
         <v>3.25676851872266</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>116</v>
       </c>
       <c r="B113" t="s">
         <v>4</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113">
         <v>3.25676851872266</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>117</v>
       </c>
       <c r="B114" t="s">
         <v>4</v>
       </c>
-      <c r="C114" t="n">
-        <v>3.46023014590009</v>
-      </c>
-    </row>
-    <row r="115">
+      <c r="C114">
+        <v>3.4602301459000899</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>118</v>
       </c>
       <c r="B115" t="s">
         <v>4</v>
       </c>
-      <c r="C115" t="n">
-        <v>3.46023014590009</v>
-      </c>
-    </row>
-    <row r="116">
+      <c r="C115">
+        <v>3.4602301459000899</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>119</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
       </c>
-      <c r="C116" t="n">
-        <v>13.6460054841937</v>
-      </c>
-    </row>
-    <row r="117">
+      <c r="C116">
+        <v>13.646005484193701</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>120</v>
       </c>
       <c r="B117" t="s">
         <v>4</v>
       </c>
-      <c r="C117" t="n">
-        <v>13.6460054841937</v>
-      </c>
-    </row>
-    <row r="118">
+      <c r="C117">
+        <v>13.646005484193701</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>121</v>
       </c>
       <c r="B118" t="s">
         <v>4</v>
       </c>
-      <c r="C118" t="n">
-        <v>16.4225834144549</v>
-      </c>
-    </row>
-    <row r="119">
+      <c r="C118">
+        <v>16.422583414454898</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>122</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
       </c>
-      <c r="C119" t="n">
-        <v>16.4225834144549</v>
-      </c>
-    </row>
-    <row r="120">
+      <c r="C119">
+        <v>16.422583414454898</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>123</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
       </c>
-      <c r="C120" t="n">
-        <v>1.94733976280201</v>
-      </c>
-    </row>
-    <row r="121">
+      <c r="C120">
+        <v>1.9473397628020099</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>124</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
       </c>
-      <c r="C121" t="n">
-        <v>1.94733976280201</v>
-      </c>
-    </row>
-    <row r="122">
+      <c r="C121">
+        <v>1.9473397628020099</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>125</v>
       </c>
       <c r="B122" t="s">
         <v>4</v>
       </c>
-      <c r="C122" t="n">
-        <v>2.02758913840313</v>
-      </c>
-    </row>
-    <row r="123">
+      <c r="C122">
+        <v>2.0275891384031302</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>126</v>
       </c>
       <c r="B123" t="s">
         <v>4</v>
       </c>
-      <c r="C123" t="n">
-        <v>2.02758913840313</v>
-      </c>
-    </row>
-    <row r="124">
+      <c r="C123">
+        <v>2.0275891384031302</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>127</v>
       </c>
       <c r="B124" t="s">
         <v>4</v>
       </c>
-      <c r="C124" t="n">
-        <v>2.49107590122785</v>
-      </c>
-    </row>
-    <row r="125">
+      <c r="C124">
+        <v>2.4910759012278501</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>128</v>
       </c>
       <c r="B125" t="s">
         <v>4</v>
       </c>
-      <c r="C125" t="n">
-        <v>2.49107590122785</v>
-      </c>
-    </row>
-    <row r="126">
+      <c r="C125">
+        <v>2.4910759012278501</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>129</v>
       </c>
       <c r="B126" t="s">
         <v>4</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126">
         <v>1.92674379251941</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>130</v>
       </c>
       <c r="B127" t="s">
         <v>4</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127">
         <v>1.92674379251941</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>131</v>
       </c>
       <c r="B128" t="s">
         <v>4</v>
       </c>
-      <c r="C128" t="n">
-        <v>6.40594235781041</v>
-      </c>
-    </row>
-    <row r="129">
+      <c r="C128">
+        <v>6.4059423578104102</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>132</v>
       </c>
       <c r="B129" t="s">
         <v>4</v>
       </c>
-      <c r="C129" t="n">
-        <v>6.40594235781041</v>
-      </c>
-    </row>
-    <row r="130">
+      <c r="C129">
+        <v>6.4059423578104102</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>133</v>
       </c>
       <c r="B130" t="s">
         <v>4</v>
       </c>
-      <c r="C130" t="n">
-        <v>5.20539976059761</v>
-      </c>
-    </row>
-    <row r="131">
+      <c r="C130">
+        <v>5.2053997605976097</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>134</v>
       </c>
       <c r="B131" t="s">
         <v>4</v>
       </c>
-      <c r="C131" t="n">
-        <v>5.20539976059761</v>
-      </c>
-    </row>
-    <row r="132">
+      <c r="C131">
+        <v>5.2053997605976097</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>135</v>
       </c>
       <c r="B132" t="s">
         <v>4</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132">
         <v>-1.49287600656777</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>136</v>
       </c>
       <c r="B133" t="s">
         <v>4</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133">
         <v>-1.49287600656777</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>137</v>
       </c>
       <c r="B134" t="s">
         <v>4</v>
       </c>
-      <c r="C134" t="n">
-        <v>15.6290628006313</v>
-      </c>
-    </row>
-    <row r="135">
+      <c r="C134">
+        <v>15.629062800631299</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>138</v>
       </c>
       <c r="B135" t="s">
         <v>4</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135">
         <v>15.6290628006312</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>139</v>
       </c>
       <c r="B136" t="s">
         <v>34</v>
       </c>
-      <c r="C136" t="n">
-        <v>0.0211080552499909</v>
-      </c>
-    </row>
-    <row r="137">
+      <c r="C136">
+        <v>2.11080552499909E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>140</v>
       </c>
       <c r="B137" t="s">
         <v>34</v>
       </c>
-      <c r="C137" t="n">
-        <v>0.0211080552499914</v>
-      </c>
-    </row>
-    <row r="138">
+      <c r="C137">
+        <v>2.11080552499914E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>141</v>
       </c>
       <c r="B138" t="s">
         <v>4</v>
       </c>
-      <c r="C138" t="n">
-        <v>1.62190869151043</v>
-      </c>
-    </row>
-    <row r="139">
+      <c r="C138">
+        <v>1.6219086915104299</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>142</v>
       </c>
       <c r="B139" t="s">
         <v>4</v>
       </c>
-      <c r="C139" t="n">
-        <v>1.62190869151043</v>
-      </c>
-    </row>
-    <row r="140">
+      <c r="C139">
+        <v>1.6219086915104299</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>143</v>
       </c>
       <c r="B140" t="s">
         <v>4</v>
       </c>
-      <c r="C140" t="n">
-        <v>6.42796039643657</v>
-      </c>
-    </row>
-    <row r="141">
+      <c r="C140">
+        <v>6.4279603964365704</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>144</v>
       </c>
       <c r="B141" t="s">
         <v>4</v>
       </c>
-      <c r="C141" t="n">
-        <v>6.42796039643656</v>
-      </c>
-    </row>
-    <row r="142">
+      <c r="C141">
+        <v>6.4279603964365597</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>145</v>
       </c>
       <c r="B142" t="s">
         <v>4</v>
       </c>
-      <c r="C142" t="n">
-        <v>3.48877756835199</v>
+      <c r="C142">
+        <v>3.4887775683519902</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C142"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2364,1569 +2383,1569 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
-        <v>2.17301857884221</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2">
+        <v>2.1730185788422101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.781738678603504</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3">
+        <v>0.78173867860350399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="n">
-        <v>2.00686335405664</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4">
+        <v>2.0068633540566401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.866162986482195</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="C5">
+        <v>-0.86616298648219503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.262112805386116</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6">
+        <v>0.26211280538611598</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.189389410759909</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
-        <v>-0.534352395703904</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="C9">
+        <v>-0.53435239570390403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
-        <v>-0.296160296305932</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10">
+        <v>-0.29616029630593199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="C12">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>-0.614198152259788</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C15">
+        <v>-0.61419815225978802</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
-      <c r="C16" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="C16">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
-      <c r="C17" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="C17">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
-      <c r="C18" t="n">
-        <v>5.99706159519149</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="C18">
+        <v>5.9970615951914903</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" t="n">
-        <v>5.911165738006</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="C19">
+        <v>5.9111657380059999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>13.8643834053898</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>6.97030307988764</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
-      <c r="C22" t="n">
-        <v>9.46082161509852</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22">
+        <v>9.4608216150985207</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>13.7458622641352</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>5.95079771501688</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
-      <c r="C25" t="n">
-        <v>4.89159000472761</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="C25">
+        <v>4.8915900047276102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
-      <c r="C26" t="n">
-        <v>4.30980864836194</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="C26">
+        <v>4.3098086483619404</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
       </c>
-      <c r="C27" t="n">
-        <v>6.39445694611415</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="C27">
+        <v>6.3944569461141496</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
-        <v>5.49094627727818</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="C28">
+        <v>5.4909462772781801</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" t="n">
-        <v>-1.43450112545477</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="C29">
+        <v>-1.4345011254547699</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
-        <v>15.6929526334756</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="C30">
+        <v>15.692952633475601</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
-      <c r="C31" t="n">
-        <v>0.0415124087045186</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="C31">
+        <v>4.1512408704518597E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
-      <c r="C32" t="n">
-        <v>1.87817476897581</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="C32">
+        <v>1.8781747689758099</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
-      <c r="C33" t="n">
-        <v>8.26899375065173</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="C33">
+        <v>8.2689937506517293</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>0.37641593570922</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>-1.36957600896864</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>1.36097553299134</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
-      <c r="C37" t="n">
-        <v>5.89060499873807</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="C37">
+        <v>5.8906049987380698</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
       </c>
-      <c r="C38" t="n">
-        <v>9.52050247725298</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="C38">
+        <v>9.5205024772529807</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>1.76061638403001</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
-      <c r="C40" t="n">
-        <v>4.98913231843714</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="C40">
+        <v>4.9891323184371403</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
         <v>4</v>
       </c>
-      <c r="C41" t="n">
-        <v>9.22347548006495</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="C41">
+        <v>9.2234754800649501</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>0.958791711254673</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
-      <c r="C43" t="n">
-        <v>9.50441872216221</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="C43">
+        <v>9.5044187221622103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
       </c>
-      <c r="C44" t="n">
-        <v>3.26315126989928</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="C44">
+        <v>3.2631512698992799</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
       </c>
-      <c r="C45" t="n">
-        <v>3.46712588787376</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="C45">
+        <v>3.4671258878737601</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>13.5923902426222</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>15.9701910795619</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
         <v>4</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>3.40371576587401</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
       </c>
-      <c r="C49" t="n">
-        <v>8.10705185679366</v>
-      </c>
-    </row>
-    <row r="50">
+      <c r="C49">
+        <v>8.1070518567936602</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
         <v>4</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>3.16918401063917</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
         <v>4</v>
       </c>
-      <c r="C51" t="n">
-        <v>3.71134665344239</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="C51">
+        <v>3.7113466534423898</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
       </c>
-      <c r="C52" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="C52">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="C53">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
         <v>4</v>
       </c>
-      <c r="C54" t="n">
-        <v>-0.534352395703903</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="C54">
+        <v>-0.53435239570390303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
         <v>4</v>
       </c>
-      <c r="C55" t="n">
-        <v>-0.534352395703905</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="C55">
+        <v>-0.53435239570390503</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
-      <c r="C56" t="n">
-        <v>-0.296160296305932</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="C56">
+        <v>-0.29616029630593199</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
         <v>4</v>
       </c>
-      <c r="C57" t="n">
-        <v>-0.296160296305931</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="C57">
+        <v>-0.29616029630593099</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
         <v>4</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
         <v>4</v>
       </c>
-      <c r="C60" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="C60">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
       </c>
-      <c r="C61" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="62">
+      <c r="C61">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
         <v>4</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
         <v>4</v>
       </c>
-      <c r="C66" t="n">
-        <v>-0.614198152259787</v>
-      </c>
-    </row>
-    <row r="67">
+      <c r="C66">
+        <v>-0.61419815225978702</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
         <v>4</v>
       </c>
-      <c r="C67" t="n">
-        <v>-0.614198152259787</v>
-      </c>
-    </row>
-    <row r="68">
+      <c r="C67">
+        <v>-0.61419815225978702</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
       </c>
-      <c r="C68" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="69">
+      <c r="C68">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
       </c>
-      <c r="C69" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="70">
+      <c r="C69">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
-      <c r="C70" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="C70">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
       </c>
-      <c r="C71" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="72">
+      <c r="C71">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
         <v>4</v>
       </c>
-      <c r="C72" t="n">
-        <v>5.99706159519149</v>
-      </c>
-    </row>
-    <row r="73">
+      <c r="C72">
+        <v>5.9970615951914903</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
-      <c r="C73" t="n">
-        <v>5.99706159519149</v>
-      </c>
-    </row>
-    <row r="74">
+      <c r="C73">
+        <v>5.9970615951914903</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
       </c>
-      <c r="C74" t="n">
-        <v>5.911165738006</v>
-      </c>
-    </row>
-    <row r="75">
+      <c r="C74">
+        <v>5.9111657380059999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
       </c>
-      <c r="C75" t="n">
-        <v>5.911165738006</v>
-      </c>
-    </row>
-    <row r="76">
+      <c r="C75">
+        <v>5.9111657380059999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>13.8643834053898</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>13.8643834053898</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>6.97030307988764</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>6.97030307988764</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
-      <c r="C80" t="n">
-        <v>9.46082161509852</v>
-      </c>
-    </row>
-    <row r="81">
+      <c r="C80">
+        <v>9.4608216150985207</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
-      <c r="C81" t="n">
-        <v>9.46082161509852</v>
-      </c>
-    </row>
-    <row r="82">
+      <c r="C81">
+        <v>9.4608216150985207</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>13.7458622641352</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>13.7458622641352</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>5.95079771501688</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>5.95079771501688</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
-      <c r="C86" t="n">
-        <v>4.89159000472761</v>
-      </c>
-    </row>
-    <row r="87">
+      <c r="C86">
+        <v>4.8915900047276102</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
-      <c r="C87" t="n">
-        <v>4.89159000472761</v>
-      </c>
-    </row>
-    <row r="88">
+      <c r="C87">
+        <v>4.8915900047276102</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
-      <c r="C88" t="n">
-        <v>4.30980864836194</v>
-      </c>
-    </row>
-    <row r="89">
+      <c r="C88">
+        <v>4.3098086483619404</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
-      <c r="C89" t="n">
-        <v>4.30980864836194</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="C89">
+        <v>4.3098086483619404</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
       </c>
-      <c r="C90" t="n">
-        <v>8.26899375065173</v>
-      </c>
-    </row>
-    <row r="91">
+      <c r="C90">
+        <v>8.2689937506517293</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
       </c>
-      <c r="C91" t="n">
-        <v>8.26899375065173</v>
-      </c>
-    </row>
-    <row r="92">
+      <c r="C91">
+        <v>8.2689937506517293</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
       </c>
-      <c r="C92" t="n">
-        <v>0.376415935709221</v>
-      </c>
-    </row>
-    <row r="93">
+      <c r="C92">
+        <v>0.37641593570922099</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>0.37641593570922</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>-1.36957600896864</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>-1.36957600896864</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>1.36097553299134</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>1.36097553299134</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
       </c>
-      <c r="C98" t="n">
-        <v>5.89060499873807</v>
-      </c>
-    </row>
-    <row r="99">
+      <c r="C98">
+        <v>5.8906049987380698</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
       </c>
-      <c r="C99" t="n">
-        <v>5.89060499873807</v>
-      </c>
-    </row>
-    <row r="100">
+      <c r="C99">
+        <v>5.8906049987380698</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100" t="s">
         <v>4</v>
       </c>
-      <c r="C100" t="n">
-        <v>9.52050247725298</v>
-      </c>
-    </row>
-    <row r="101">
+      <c r="C100">
+        <v>9.5205024772529807</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>104</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
       </c>
-      <c r="C101" t="n">
-        <v>9.52050247725298</v>
-      </c>
-    </row>
-    <row r="102">
+      <c r="C101">
+        <v>9.5205024772529807</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>105</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>1.76061638403001</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>106</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>1.76061638403001</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>107</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
       </c>
-      <c r="C104" t="n">
-        <v>4.98913231843714</v>
-      </c>
-    </row>
-    <row r="105">
+      <c r="C104">
+        <v>4.9891323184371403</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>108</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
-      <c r="C105" t="n">
-        <v>4.98913231843714</v>
-      </c>
-    </row>
-    <row r="106">
+      <c r="C105">
+        <v>4.9891323184371403</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>109</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
-      <c r="C106" t="n">
-        <v>9.22347548006495</v>
-      </c>
-    </row>
-    <row r="107">
+      <c r="C106">
+        <v>9.2234754800649501</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>110</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
-      <c r="C107" t="n">
-        <v>9.22347548006495</v>
-      </c>
-    </row>
-    <row r="108">
+      <c r="C107">
+        <v>9.2234754800649501</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>111</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>0.958791711254673</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>112</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109">
         <v>0.958791711254673</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>113</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
-      <c r="C110" t="n">
-        <v>9.5044187221622</v>
-      </c>
-    </row>
-    <row r="111">
+      <c r="C110">
+        <v>9.5044187221621996</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>114</v>
       </c>
       <c r="B111" t="s">
         <v>4</v>
       </c>
-      <c r="C111" t="n">
-        <v>9.5044187221622</v>
-      </c>
-    </row>
-    <row r="112">
+      <c r="C111">
+        <v>9.5044187221621996</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>115</v>
       </c>
       <c r="B112" t="s">
         <v>4</v>
       </c>
-      <c r="C112" t="n">
-        <v>3.26315126989928</v>
-      </c>
-    </row>
-    <row r="113">
+      <c r="C112">
+        <v>3.2631512698992799</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>116</v>
       </c>
       <c r="B113" t="s">
         <v>4</v>
       </c>
-      <c r="C113" t="n">
-        <v>3.26315126989928</v>
-      </c>
-    </row>
-    <row r="114">
+      <c r="C113">
+        <v>3.2631512698992799</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>117</v>
       </c>
       <c r="B114" t="s">
         <v>4</v>
       </c>
-      <c r="C114" t="n">
-        <v>3.46712588787375</v>
-      </c>
-    </row>
-    <row r="115">
+      <c r="C114">
+        <v>3.4671258878737499</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>118</v>
       </c>
       <c r="B115" t="s">
         <v>4</v>
       </c>
-      <c r="C115" t="n">
-        <v>3.46712588787375</v>
-      </c>
-    </row>
-    <row r="116">
+      <c r="C115">
+        <v>3.4671258878737499</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>119</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116">
         <v>13.5923902426222</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>120</v>
       </c>
       <c r="B117" t="s">
         <v>4</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117">
         <v>13.5923902426222</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>121</v>
       </c>
       <c r="B118" t="s">
         <v>4</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118">
         <v>15.9701910795619</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>122</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119">
         <v>15.9701910795619</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>123</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120">
         <v>3.40371576587401</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>124</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121">
         <v>3.40371576587401</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>125</v>
       </c>
       <c r="B122" t="s">
         <v>4</v>
       </c>
-      <c r="C122" t="n">
-        <v>8.10705185679367</v>
-      </c>
-    </row>
-    <row r="123">
+      <c r="C122">
+        <v>8.1070518567936691</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>126</v>
       </c>
       <c r="B123" t="s">
         <v>4</v>
       </c>
-      <c r="C123" t="n">
-        <v>8.10705185679367</v>
-      </c>
-    </row>
-    <row r="124">
+      <c r="C123">
+        <v>8.1070518567936691</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>127</v>
       </c>
       <c r="B124" t="s">
         <v>4</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124">
         <v>3.16918401063917</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>128</v>
       </c>
       <c r="B125" t="s">
         <v>4</v>
       </c>
-      <c r="C125" t="n">
-        <v>3.16918401063916</v>
-      </c>
-    </row>
-    <row r="126">
+      <c r="C125">
+        <v>3.1691840106391602</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>129</v>
       </c>
       <c r="B126" t="s">
         <v>4</v>
       </c>
-      <c r="C126" t="n">
-        <v>3.71134665344239</v>
-      </c>
-    </row>
-    <row r="127">
+      <c r="C126">
+        <v>3.7113466534423898</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>130</v>
       </c>
       <c r="B127" t="s">
         <v>4</v>
       </c>
-      <c r="C127" t="n">
-        <v>3.71134665344239</v>
-      </c>
-    </row>
-    <row r="128">
+      <c r="C127">
+        <v>3.7113466534423898</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>131</v>
       </c>
       <c r="B128" t="s">
         <v>4</v>
       </c>
-      <c r="C128" t="n">
-        <v>6.39445694611415</v>
-      </c>
-    </row>
-    <row r="129">
+      <c r="C128">
+        <v>6.3944569461141496</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>132</v>
       </c>
       <c r="B129" t="s">
         <v>4</v>
       </c>
-      <c r="C129" t="n">
-        <v>6.39445694611415</v>
-      </c>
-    </row>
-    <row r="130">
+      <c r="C129">
+        <v>6.3944569461141496</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>133</v>
       </c>
       <c r="B130" t="s">
         <v>4</v>
       </c>
-      <c r="C130" t="n">
-        <v>5.49094627727818</v>
-      </c>
-    </row>
-    <row r="131">
+      <c r="C130">
+        <v>5.4909462772781801</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>134</v>
       </c>
       <c r="B131" t="s">
         <v>4</v>
       </c>
-      <c r="C131" t="n">
-        <v>5.49094627727819</v>
-      </c>
-    </row>
-    <row r="132">
+      <c r="C131">
+        <v>5.4909462772781898</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>135</v>
       </c>
       <c r="B132" t="s">
         <v>4</v>
       </c>
-      <c r="C132" t="n">
-        <v>-1.43450112545477</v>
-      </c>
-    </row>
-    <row r="133">
+      <c r="C132">
+        <v>-1.4345011254547699</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>136</v>
       </c>
       <c r="B133" t="s">
         <v>4</v>
       </c>
-      <c r="C133" t="n">
-        <v>-1.43450112545477</v>
-      </c>
-    </row>
-    <row r="134">
+      <c r="C133">
+        <v>-1.4345011254547699</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>137</v>
       </c>
       <c r="B134" t="s">
         <v>4</v>
       </c>
-      <c r="C134" t="n">
-        <v>15.6929526334756</v>
-      </c>
-    </row>
-    <row r="135">
+      <c r="C134">
+        <v>15.692952633475601</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>138</v>
       </c>
       <c r="B135" t="s">
         <v>4</v>
       </c>
-      <c r="C135" t="n">
-        <v>15.6929526334756</v>
-      </c>
-    </row>
-    <row r="136">
+      <c r="C135">
+        <v>15.692952633475601</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>139</v>
       </c>
       <c r="B136" t="s">
         <v>34</v>
       </c>
-      <c r="C136" t="n">
-        <v>0.0415124087045188</v>
-      </c>
-    </row>
-    <row r="137">
+      <c r="C136">
+        <v>4.1512408704518798E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>140</v>
       </c>
       <c r="B137" t="s">
         <v>34</v>
       </c>
-      <c r="C137" t="n">
-        <v>0.0415124087045194</v>
-      </c>
-    </row>
-    <row r="138">
+      <c r="C137">
+        <v>4.1512408704519402E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>141</v>
       </c>
       <c r="B138" t="s">
         <v>4</v>
       </c>
-      <c r="C138" t="n">
-        <v>1.87817476897581</v>
-      </c>
-    </row>
-    <row r="139">
+      <c r="C138">
+        <v>1.8781747689758099</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>142</v>
       </c>
       <c r="B139" t="s">
         <v>4</v>
       </c>
-      <c r="C139" t="n">
-        <v>1.87817476897581</v>
-      </c>
-    </row>
-    <row r="140">
+      <c r="C139">
+        <v>1.8781747689758099</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>143</v>
       </c>
       <c r="B140" t="s">
         <v>4</v>
       </c>
-      <c r="C140" t="n">
-        <v>6.43044786872114</v>
-      </c>
-    </row>
-    <row r="141">
+      <c r="C140">
+        <v>6.4304478687211404</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>144</v>
       </c>
       <c r="B141" t="s">
         <v>4</v>
       </c>
-      <c r="C141" t="n">
-        <v>6.43044786872114</v>
-      </c>
-    </row>
-    <row r="142">
+      <c r="C141">
+        <v>6.4304478687211404</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>145</v>
       </c>
       <c r="B142" t="s">
         <v>4</v>
       </c>
-      <c r="C142" t="n">
-        <v>4.0811896424821</v>
+      <c r="C142">
+        <v>4.0811896424820997</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:C142"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3937,1559 +3956,1559 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
-        <v>2.17301857884221</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2">
+        <v>2.1730185788422101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.781738678603504</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3">
+        <v>0.78173867860350399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="n">
-        <v>2.00686335405664</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4">
+        <v>2.0068633540566401</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.866162986482195</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="C5">
+        <v>-0.86616298648219503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.262112805386116</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6">
+        <v>0.26211280538611598</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>0.189389410759909</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="C8" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C9" t="n">
-        <v>-0.534352395703904</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="C9">
+        <v>-0.53435239570390403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
       </c>
-      <c r="C10" t="n">
-        <v>-0.296160296305932</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10">
+        <v>-0.29616029630593199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="C12">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>-0.614198152259788</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C15">
+        <v>-0.61419815225978802</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
       </c>
-      <c r="C16" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="C16">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
       </c>
-      <c r="C17" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="C17">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
       </c>
-      <c r="C18" t="n">
-        <v>5.44336172228399</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="C18">
+        <v>5.4433617222839903</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" t="n">
-        <v>6.78089554882231</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="C19">
+        <v>6.7808955488223104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>10.9570408303106</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
       </c>
-      <c r="C21" t="n">
-        <v>6.19224175844022</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="C21">
+        <v>6.1922417584402201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
-      <c r="C22" t="n">
-        <v>5.00021737024191</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22">
+        <v>5.0002173702419102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
-        <v>10.5296793090833</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="C23">
+        <v>10.529679309083299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
-        <v>5.46098072522364</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="C24">
+        <v>5.4609807252236404</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>5.58836272287685</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
       </c>
-      <c r="C26" t="n">
-        <v>4.25721471564939</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="C26">
+        <v>4.2572147156493898</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
       </c>
-      <c r="C27" t="n">
-        <v>5.94945068855246</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="C27">
+        <v>5.9494506885524601</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
       </c>
-      <c r="C28" t="n">
-        <v>5.4233143752514</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="C28">
+        <v>5.4233143752514001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" t="n">
-        <v>-1.49146059310908</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="C29">
+        <v>-1.4914605931090801</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>32</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>15.6283669550079</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
       </c>
-      <c r="C31" t="n">
-        <v>0.0237343141310128</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="C31">
+        <v>2.3734314131012801E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
-      <c r="C32" t="n">
-        <v>1.6237671622627</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="C32">
+        <v>1.6237671622626999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
-      <c r="C33" t="n">
-        <v>-0.664360472583396</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="C33">
+        <v>-0.66436047258339603</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>37</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>2.47456094769705</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>38</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
-      <c r="C35" t="n">
-        <v>-1.37639149931007</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="C35">
+        <v>-1.3763914993100701</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>39</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
-      <c r="C36" t="n">
-        <v>1.37436394023385</v>
-      </c>
-    </row>
-    <row r="37">
+      <c r="C36">
+        <v>1.3743639402338499</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
-      <c r="C37" t="n">
-        <v>0.251641531424963</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="C37">
+        <v>0.25164153142496298</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
       </c>
-      <c r="C38" t="n">
-        <v>7.37533802678267</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="C38">
+        <v>7.3753380267826696</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>42</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>1.77236282861549</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>43</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
-      <c r="C40" t="n">
-        <v>0.174737651323263</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="C40">
+        <v>0.17473765132326299</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>44</v>
       </c>
       <c r="B41" t="s">
         <v>4</v>
       </c>
-      <c r="C41" t="n">
-        <v>7.20697676560961</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="C41">
+        <v>7.2069767656096104</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>1.00451858341518</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>46</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
-      <c r="C43" t="n">
-        <v>4.14200762570001</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="C43">
+        <v>4.1420076257000096</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
       </c>
-      <c r="C44" t="n">
-        <v>3.31213102953293</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="C44">
+        <v>3.3121310295329298</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>48</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
       </c>
-      <c r="C45" t="n">
-        <v>3.61574705247611</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="C45">
+        <v>3.6157470524761099</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>49</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>13.8045240736841</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>50</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
       </c>
-      <c r="C47" t="n">
-        <v>16.6584939586896</v>
-      </c>
-    </row>
-    <row r="48">
+      <c r="C47">
+        <v>16.658493958689601</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>51</v>
       </c>
       <c r="B48" t="s">
         <v>4</v>
       </c>
-      <c r="C48" t="n">
-        <v>2.87985854522987</v>
-      </c>
-    </row>
-    <row r="49">
+      <c r="C48">
+        <v>2.8798585452298702</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>52</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
       </c>
-      <c r="C49" t="n">
-        <v>3.02297571700372</v>
-      </c>
-    </row>
-    <row r="50">
+      <c r="C49">
+        <v>3.0229757170037201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>53</v>
       </c>
       <c r="B50" t="s">
         <v>4</v>
       </c>
-      <c r="C50" t="n">
-        <v>2.84290216863513</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="C50">
+        <v>2.8429021686351299</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>54</v>
       </c>
       <c r="B51" t="s">
         <v>4</v>
       </c>
-      <c r="C51" t="n">
-        <v>2.89869903991406</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="C51">
+        <v>2.8986990399140602</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>55</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
       </c>
-      <c r="C52" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="C52">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>56</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
-        <v>3.92701712304009</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="C53">
+        <v>3.9270171230400899</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>57</v>
       </c>
       <c r="B54" t="s">
         <v>4</v>
       </c>
-      <c r="C54" t="n">
-        <v>-0.534352395703903</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="C54">
+        <v>-0.53435239570390303</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>58</v>
       </c>
       <c r="B55" t="s">
         <v>4</v>
       </c>
-      <c r="C55" t="n">
-        <v>-0.534352395703905</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="C55">
+        <v>-0.53435239570390503</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>59</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
-      <c r="C56" t="n">
-        <v>-0.296160296305932</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="C56">
+        <v>-0.29616029630593199</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>60</v>
       </c>
       <c r="B57" t="s">
         <v>4</v>
       </c>
-      <c r="C57" t="n">
-        <v>-0.296160296305931</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="C57">
+        <v>-0.29616029630593099</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>61</v>
       </c>
       <c r="B58" t="s">
         <v>4</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>62</v>
       </c>
       <c r="B59" t="s">
         <v>4</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>1.66356916338087</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>63</v>
       </c>
       <c r="B60" t="s">
         <v>4</v>
       </c>
-      <c r="C60" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="C60">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>64</v>
       </c>
       <c r="B61" t="s">
         <v>4</v>
       </c>
-      <c r="C61" t="n">
-        <v>2.01866181190736</v>
-      </c>
-    </row>
-    <row r="62">
+      <c r="C61">
+        <v>2.0186618119073598</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>65</v>
       </c>
       <c r="B62" t="s">
         <v>4</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>66</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>1.11838120514126</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>67</v>
       </c>
       <c r="B64" t="s">
         <v>4</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>68</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>2.1535439501211</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>69</v>
       </c>
       <c r="B66" t="s">
         <v>4</v>
       </c>
-      <c r="C66" t="n">
-        <v>-0.614198152259787</v>
-      </c>
-    </row>
-    <row r="67">
+      <c r="C66">
+        <v>-0.61419815225978702</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>70</v>
       </c>
       <c r="B67" t="s">
         <v>4</v>
       </c>
-      <c r="C67" t="n">
-        <v>-0.614198152259787</v>
-      </c>
-    </row>
-    <row r="68">
+      <c r="C67">
+        <v>-0.61419815225978702</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>71</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
       </c>
-      <c r="C68" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="69">
+      <c r="C68">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>72</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
       </c>
-      <c r="C69" t="n">
-        <v>2.27374916500553</v>
-      </c>
-    </row>
-    <row r="70">
+      <c r="C69">
+        <v>2.2737491650055301</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>73</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
-      <c r="C70" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="C70">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>74</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
       </c>
-      <c r="C71" t="n">
-        <v>4.25239757909376</v>
-      </c>
-    </row>
-    <row r="72">
+      <c r="C71">
+        <v>4.2523975790937598</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>75</v>
       </c>
       <c r="B72" t="s">
         <v>4</v>
       </c>
-      <c r="C72" t="n">
-        <v>5.44336172228399</v>
-      </c>
-    </row>
-    <row r="73">
+      <c r="C72">
+        <v>5.4433617222839903</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>76</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
-      <c r="C73" t="n">
-        <v>5.44336172228399</v>
-      </c>
-    </row>
-    <row r="74">
+      <c r="C73">
+        <v>5.4433617222839903</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>77</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
       </c>
-      <c r="C74" t="n">
-        <v>6.78089554882231</v>
-      </c>
-    </row>
-    <row r="75">
+      <c r="C74">
+        <v>6.7808955488223104</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>78</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
       </c>
-      <c r="C75" t="n">
-        <v>6.78089554882231</v>
-      </c>
-    </row>
-    <row r="76">
+      <c r="C75">
+        <v>6.7808955488223104</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>79</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>10.9570408303106</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>80</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>10.9570408303106</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>81</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
       </c>
-      <c r="C78" t="n">
-        <v>6.19224175844021</v>
-      </c>
-    </row>
-    <row r="79">
+      <c r="C78">
+        <v>6.1922417584402103</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>82</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
       </c>
-      <c r="C79" t="n">
-        <v>6.19224175844022</v>
-      </c>
-    </row>
-    <row r="80">
+      <c r="C79">
+        <v>6.1922417584402201</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>83</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
       </c>
-      <c r="C80" t="n">
-        <v>5.0002173702419</v>
-      </c>
-    </row>
-    <row r="81">
+      <c r="C80">
+        <v>5.0002173702419004</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>84</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
       </c>
-      <c r="C81" t="n">
-        <v>5.00021737024191</v>
-      </c>
-    </row>
-    <row r="82">
+      <c r="C81">
+        <v>5.0002173702419102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>85</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
       </c>
-      <c r="C82" t="n">
-        <v>10.5296793090833</v>
-      </c>
-    </row>
-    <row r="83">
+      <c r="C82">
+        <v>10.529679309083299</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>86</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
       </c>
-      <c r="C83" t="n">
-        <v>10.5296793090833</v>
-      </c>
-    </row>
-    <row r="84">
+      <c r="C83">
+        <v>10.529679309083299</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>87</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
       </c>
-      <c r="C84" t="n">
-        <v>5.46098072522364</v>
-      </c>
-    </row>
-    <row r="85">
+      <c r="C84">
+        <v>5.4609807252236404</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>88</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
       </c>
-      <c r="C85" t="n">
-        <v>5.46098072522364</v>
-      </c>
-    </row>
-    <row r="86">
+      <c r="C85">
+        <v>5.4609807252236404</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>89</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
       </c>
-      <c r="C86" t="n">
-        <v>5.58836272287686</v>
-      </c>
-    </row>
-    <row r="87">
+      <c r="C86">
+        <v>5.5883627228768598</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>90</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>5.58836272287685</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>91</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
-      <c r="C88" t="n">
-        <v>4.25721471564939</v>
-      </c>
-    </row>
-    <row r="89">
+      <c r="C88">
+        <v>4.2572147156493898</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>92</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
       </c>
-      <c r="C89" t="n">
-        <v>4.25721471564939</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="C89">
+        <v>4.2572147156493898</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>93</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
       </c>
-      <c r="C90" t="n">
-        <v>-0.664360472583396</v>
-      </c>
-    </row>
-    <row r="91">
+      <c r="C90">
+        <v>-0.66436047258339603</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>94</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
       </c>
-      <c r="C91" t="n">
-        <v>-0.664360472583395</v>
-      </c>
-    </row>
-    <row r="92">
+      <c r="C91">
+        <v>-0.66436047258339503</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>95</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>2.47456094769705</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>96</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>2.47456094769705</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>97</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
-      <c r="C94" t="n">
-        <v>-1.37639149931007</v>
-      </c>
-    </row>
-    <row r="95">
+      <c r="C94">
+        <v>-1.3763914993100701</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>98</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
       </c>
-      <c r="C95" t="n">
-        <v>-1.37639149931007</v>
-      </c>
-    </row>
-    <row r="96">
+      <c r="C95">
+        <v>-1.3763914993100701</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>99</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
       </c>
-      <c r="C96" t="n">
-        <v>1.37436394023385</v>
-      </c>
-    </row>
-    <row r="97">
+      <c r="C96">
+        <v>1.3743639402338499</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>100</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
-      <c r="C97" t="n">
-        <v>1.37436394023385</v>
-      </c>
-    </row>
-    <row r="98">
+      <c r="C97">
+        <v>1.3743639402338499</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>101</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
       </c>
-      <c r="C98" t="n">
-        <v>0.251641531424963</v>
-      </c>
-    </row>
-    <row r="99">
+      <c r="C98">
+        <v>0.25164153142496298</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>102</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
       </c>
-      <c r="C99" t="n">
-        <v>0.251641531424963</v>
-      </c>
-    </row>
-    <row r="100">
+      <c r="C99">
+        <v>0.25164153142496298</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>103</v>
       </c>
       <c r="B100" t="s">
         <v>4</v>
       </c>
-      <c r="C100" t="n">
-        <v>7.37533802678267</v>
-      </c>
-    </row>
-    <row r="101">
+      <c r="C100">
+        <v>7.3753380267826696</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>104</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
       </c>
-      <c r="C101" t="n">
-        <v>7.37533802678267</v>
-      </c>
-    </row>
-    <row r="102">
+      <c r="C101">
+        <v>7.3753380267826696</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>105</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>1.77236282861549</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>106</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>1.77236282861549</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>107</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
       </c>
-      <c r="C104" t="n">
-        <v>0.174737651323262</v>
-      </c>
-    </row>
-    <row r="105">
+      <c r="C104">
+        <v>0.17473765132326199</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>108</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
-      <c r="C105" t="n">
-        <v>0.174737651323263</v>
-      </c>
-    </row>
-    <row r="106">
+      <c r="C105">
+        <v>0.17473765132326299</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>109</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
-      <c r="C106" t="n">
-        <v>7.20697676560961</v>
-      </c>
-    </row>
-    <row r="107">
+      <c r="C106">
+        <v>7.2069767656096104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>110</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
-      <c r="C107" t="n">
-        <v>7.20697676560961</v>
-      </c>
-    </row>
-    <row r="108">
+      <c r="C107">
+        <v>7.2069767656096104</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>111</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108">
         <v>1.00451858341518</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>112</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109">
         <v>1.00451858341518</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>113</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
-      <c r="C110" t="n">
-        <v>4.14200762570001</v>
-      </c>
-    </row>
-    <row r="111">
+      <c r="C110">
+        <v>4.1420076257000096</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>114</v>
       </c>
       <c r="B111" t="s">
         <v>4</v>
       </c>
-      <c r="C111" t="n">
-        <v>4.14200762570002</v>
-      </c>
-    </row>
-    <row r="112">
+      <c r="C111">
+        <v>4.1420076257000202</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>115</v>
       </c>
       <c r="B112" t="s">
         <v>4</v>
       </c>
-      <c r="C112" t="n">
-        <v>3.31213102953293</v>
-      </c>
-    </row>
-    <row r="113">
+      <c r="C112">
+        <v>3.3121310295329298</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>116</v>
       </c>
       <c r="B113" t="s">
         <v>4</v>
       </c>
-      <c r="C113" t="n">
-        <v>3.31213102953293</v>
-      </c>
-    </row>
-    <row r="114">
+      <c r="C113">
+        <v>3.3121310295329298</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>117</v>
       </c>
       <c r="B114" t="s">
         <v>4</v>
       </c>
-      <c r="C114" t="n">
-        <v>3.61574705247611</v>
-      </c>
-    </row>
-    <row r="115">
+      <c r="C114">
+        <v>3.6157470524761099</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>118</v>
       </c>
       <c r="B115" t="s">
         <v>4</v>
       </c>
-      <c r="C115" t="n">
-        <v>3.61574705247611</v>
-      </c>
-    </row>
-    <row r="116">
+      <c r="C115">
+        <v>3.6157470524761099</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>119</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116">
         <v>13.8045240736841</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>120</v>
       </c>
       <c r="B117" t="s">
         <v>4</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117">
         <v>13.8045240736841</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>121</v>
       </c>
       <c r="B118" t="s">
         <v>4</v>
       </c>
-      <c r="C118" t="n">
-        <v>16.6584939586896</v>
-      </c>
-    </row>
-    <row r="119">
+      <c r="C118">
+        <v>16.658493958689601</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>122</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
       </c>
-      <c r="C119" t="n">
-        <v>16.6584939586896</v>
-      </c>
-    </row>
-    <row r="120">
+      <c r="C119">
+        <v>16.658493958689601</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>123</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
       </c>
-      <c r="C120" t="n">
-        <v>2.87985854522987</v>
-      </c>
-    </row>
-    <row r="121">
+      <c r="C120">
+        <v>2.8798585452298702</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>124</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
       </c>
-      <c r="C121" t="n">
-        <v>2.87985854522987</v>
-      </c>
-    </row>
-    <row r="122">
+      <c r="C121">
+        <v>2.8798585452298702</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>125</v>
       </c>
       <c r="B122" t="s">
         <v>4</v>
       </c>
-      <c r="C122" t="n">
-        <v>3.02297571700372</v>
-      </c>
-    </row>
-    <row r="123">
+      <c r="C122">
+        <v>3.0229757170037201</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>126</v>
       </c>
       <c r="B123" t="s">
         <v>4</v>
       </c>
-      <c r="C123" t="n">
-        <v>3.02297571700372</v>
-      </c>
-    </row>
-    <row r="124">
+      <c r="C123">
+        <v>3.0229757170037201</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>127</v>
       </c>
       <c r="B124" t="s">
         <v>4</v>
       </c>
-      <c r="C124" t="n">
-        <v>2.84290216863513</v>
-      </c>
-    </row>
-    <row r="125">
+      <c r="C124">
+        <v>2.8429021686351299</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>128</v>
       </c>
       <c r="B125" t="s">
         <v>4</v>
       </c>
-      <c r="C125" t="n">
-        <v>2.84290216863513</v>
-      </c>
-    </row>
-    <row r="126">
+      <c r="C125">
+        <v>2.8429021686351299</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>129</v>
       </c>
       <c r="B126" t="s">
         <v>4</v>
       </c>
-      <c r="C126" t="n">
-        <v>2.89869903991406</v>
-      </c>
-    </row>
-    <row r="127">
+      <c r="C126">
+        <v>2.8986990399140602</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>130</v>
       </c>
       <c r="B127" t="s">
         <v>4</v>
       </c>
-      <c r="C127" t="n">
-        <v>2.89869903991406</v>
-      </c>
-    </row>
-    <row r="128">
+      <c r="C127">
+        <v>2.8986990399140602</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>131</v>
       </c>
       <c r="B128" t="s">
         <v>4</v>
       </c>
-      <c r="C128" t="n">
-        <v>5.94945068855246</v>
-      </c>
-    </row>
-    <row r="129">
+      <c r="C128">
+        <v>5.9494506885524601</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>132</v>
       </c>
       <c r="B129" t="s">
         <v>4</v>
       </c>
-      <c r="C129" t="n">
-        <v>5.94945068855246</v>
-      </c>
-    </row>
-    <row r="130">
+      <c r="C129">
+        <v>5.9494506885524601</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>133</v>
       </c>
       <c r="B130" t="s">
         <v>4</v>
       </c>
-      <c r="C130" t="n">
-        <v>5.42331437525139</v>
-      </c>
-    </row>
-    <row r="131">
+      <c r="C130">
+        <v>5.4233143752513904</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>134</v>
       </c>
       <c r="B131" t="s">
         <v>4</v>
       </c>
-      <c r="C131" t="n">
-        <v>5.4233143752514</v>
-      </c>
-    </row>
-    <row r="132">
+      <c r="C131">
+        <v>5.4233143752514001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>135</v>
       </c>
       <c r="B132" t="s">
         <v>4</v>
       </c>
-      <c r="C132" t="n">
-        <v>-1.49146059310908</v>
-      </c>
-    </row>
-    <row r="133">
+      <c r="C132">
+        <v>-1.4914605931090801</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>136</v>
       </c>
       <c r="B133" t="s">
         <v>4</v>
       </c>
-      <c r="C133" t="n">
-        <v>-1.49146059310908</v>
-      </c>
-    </row>
-    <row r="134">
+      <c r="C133">
+        <v>-1.4914605931090801</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>137</v>
       </c>
       <c r="B134" t="s">
         <v>4</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134">
         <v>15.628366955008</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>138</v>
       </c>
       <c r="B135" t="s">
         <v>4</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135">
         <v>15.628366955008</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>139</v>
       </c>
       <c r="B136" t="s">
         <v>34</v>
       </c>
-      <c r="C136" t="n">
-        <v>0.0237343141310134</v>
-      </c>
-    </row>
-    <row r="137">
+      <c r="C136">
+        <v>2.3734314131013401E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>140</v>
       </c>
       <c r="B137" t="s">
         <v>34</v>
       </c>
-      <c r="C137" t="n">
-        <v>0.0237343141310123</v>
-      </c>
-    </row>
-    <row r="138">
+      <c r="C137">
+        <v>2.3734314131012301E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>141</v>
       </c>
       <c r="B138" t="s">
         <v>4</v>
       </c>
-      <c r="C138" t="n">
-        <v>1.6237671622627</v>
-      </c>
-    </row>
-    <row r="139">
+      <c r="C138">
+        <v>1.6237671622626999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>142</v>
       </c>
       <c r="B139" t="s">
         <v>4</v>
       </c>
-      <c r="C139" t="n">
-        <v>1.6237671622627</v>
-      </c>
-    </row>
-    <row r="140">
+      <c r="C139">
+        <v>1.6237671622626999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>143</v>
       </c>
       <c r="B140" t="s">
         <v>4</v>
       </c>
-      <c r="C140" t="n">
-        <v>5.80278853203374</v>
-      </c>
-    </row>
-    <row r="141">
+      <c r="C140">
+        <v>5.8027885320337402</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>144</v>
       </c>
       <c r="B141" t="s">
         <v>4</v>
       </c>
-      <c r="C141" t="n">
-        <v>5.80278853203374</v>
-      </c>
-    </row>
-    <row r="142">
+      <c r="C141">
+        <v>5.8027885320337402</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>145</v>
       </c>
       <c r="B142" t="s">
         <v>4</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142">
         <v>3.37124270122683</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>